--- a/Result/profitability/8996.xlsx
+++ b/Result/profitability/8996.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>2.42</v>
+        <v>2.40625</v>
       </c>
       <c r="N2" t="n">
-        <v>28.3075</v>
+        <v>27.38</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2025</v>
+        <v>2.34625</v>
       </c>
       <c r="N3" t="n">
-        <v>27.845</v>
+        <v>28.04625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>2.15625</v>
+        <v>2.24375</v>
       </c>
       <c r="N4" t="n">
-        <v>28.27125</v>
+        <v>27.7675</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>1.97875</v>
+        <v>2.08125</v>
       </c>
       <c r="N5" t="n">
-        <v>27.50625</v>
+        <v>27.0875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8225</v>
+        <v>1.73875</v>
       </c>
       <c r="N6" t="n">
-        <v>26.7975</v>
+        <v>26.9525</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.76</v>
       </c>
       <c r="M7" t="n">
-        <v>1.24875</v>
+        <v>1.0875</v>
       </c>
       <c r="N7" t="n">
-        <v>25.89375</v>
+        <v>25.7875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7837500000000002</v>
+        <v>0.23625</v>
       </c>
       <c r="N8" t="n">
-        <v>24.90125</v>
+        <v>24.52375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2305</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1706</v>
+      </c>
+      <c r="E75" t="n">
+        <v>599</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>298</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.94%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>293</v>
+      </c>
+      <c r="K75" t="n">
+        <v>201</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.6325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.9775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6697247706422018</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.104066161268091</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6119402985074627</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.350000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1141396933560478</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
